--- a/Optimized_Schedule.xlsx
+++ b/Optimized_Schedule.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Group_code</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -481,22 +481,27 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Min_Hours</t>
+          <t>OT</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Max_Hours</t>
+          <t>UT</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>OT</t>
+          <t>Base_Pay</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>UT</t>
+          <t>OT_Pay</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Total_Pay</t>
         </is>
       </c>
     </row>
@@ -513,32 +518,32 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Night</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Night</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -547,19 +552,22 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="K2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>8000</v>
       </c>
     </row>
     <row r="3">
@@ -580,22 +588,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Night</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -609,19 +617,22 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="K3" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>8000</v>
       </c>
     </row>
     <row r="4">
@@ -637,32 +648,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Morning</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>Evening</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>Night</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Off</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -674,16 +685,19 @@
         <v>40</v>
       </c>
       <c r="K4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>20000</v>
       </c>
     </row>
     <row r="5">
@@ -699,22 +713,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -724,7 +738,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Night</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -733,19 +747,22 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="K5" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>16000</v>
       </c>
     </row>
     <row r="6">
@@ -761,12 +778,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Morning</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -776,12 +793,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Morning</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Night</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,16 +815,19 @@
         <v>32</v>
       </c>
       <c r="K6" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>16000</v>
       </c>
     </row>
     <row r="7">
@@ -823,7 +843,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Morning</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -833,12 +853,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Night</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -860,16 +880,19 @@
         <v>32</v>
       </c>
       <c r="K7" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>16000</v>
       </c>
     </row>
     <row r="8">
@@ -885,7 +908,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -895,22 +918,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Morning</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Morning</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -919,19 +942,22 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="K8" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>20000</v>
       </c>
     </row>
     <row r="9">
@@ -947,7 +973,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -957,22 +983,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Night</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Night</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -981,18 +1007,21 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1009,22 +1038,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Night</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Morning</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1034,7 +1063,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1046,16 +1075,19 @@
         <v>32</v>
       </c>
       <c r="K10" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>16000</v>
       </c>
     </row>
     <row r="11">
@@ -1076,17 +1108,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1105,19 +1137,22 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>12000</v>
       </c>
     </row>
     <row r="12">
@@ -1133,27 +1168,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Night</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1167,18 +1202,21 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1195,7 +1233,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Morning</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1210,17 +1248,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Night</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1232,16 +1270,19 @@
         <v>40</v>
       </c>
       <c r="K13" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>20000</v>
       </c>
     </row>
     <row r="14">
@@ -1257,32 +1298,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Night</t>
+          <t>Morning</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Night</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1291,19 +1332,22 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="K14" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>12000</v>
       </c>
     </row>
     <row r="15">
@@ -1319,12 +1363,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Night</t>
+          <t>Morning</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1334,12 +1378,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Night</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1353,19 +1397,22 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="K15" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>12000</v>
       </c>
     </row>
     <row r="16">
@@ -1386,27 +1433,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1415,18 +1462,21 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1443,7 +1493,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Night</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1453,22 +1503,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1477,19 +1527,22 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="K17" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>4000</v>
       </c>
     </row>
     <row r="18">
@@ -1510,22 +1563,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Morning</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1539,19 +1592,22 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="K18" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>4000</v>
       </c>
     </row>
     <row r="19">
@@ -1567,29 +1623,29 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>Evening</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>Night</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Evening</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Off</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Night</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Morning</t>
-        </is>
-      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Off</t>
@@ -1601,19 +1657,22 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="K19" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>8000</v>
       </c>
     </row>
     <row r="20">
@@ -1629,27 +1688,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Night</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1663,18 +1722,21 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1696,17 +1758,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Night</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1716,7 +1778,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1725,19 +1787,22 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="K21" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>4000</v>
       </c>
     </row>
     <row r="22">
@@ -1753,7 +1818,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1763,7 +1828,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Night</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1773,33 +1838,36 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="K22" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>16000</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>16000</v>
       </c>
     </row>
     <row r="23">
@@ -1815,7 +1883,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1825,12 +1893,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1840,28 +1908,31 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Night</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="K23" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="L23" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>9000</v>
+      </c>
+      <c r="O23" t="n">
+        <v>21000</v>
       </c>
     </row>
     <row r="24">
@@ -1882,48 +1953,51 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="K24" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="L24" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>8</v>
+        <v>4000</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3000</v>
+      </c>
+      <c r="O24" t="n">
+        <v>7000</v>
       </c>
     </row>
     <row r="25">
@@ -1939,12 +2013,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Night</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1954,7 +2028,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Morning</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1969,23 +2043,26 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="J25" t="n">
         <v>40</v>
       </c>
       <c r="K25" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>20000</v>
       </c>
     </row>
     <row r="26">
@@ -2001,17 +2078,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Night</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Night</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2021,33 +2098,36 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Morning</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="K26" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>8000</v>
       </c>
     </row>
     <row r="27">
@@ -2068,12 +2148,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2088,28 +2168,31 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Night</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="K27" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>4000</v>
       </c>
     </row>
     <row r="28">
@@ -2130,17 +2213,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2150,7 +2233,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2159,19 +2242,22 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="K28" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>4000</v>
       </c>
     </row>
     <row r="29">
@@ -2187,53 +2273,56 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Evening</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
           <t>Night</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Evening</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Night</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Off</t>
-        </is>
-      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>Off</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="K29" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>8000</v>
       </c>
     </row>
     <row r="30">
@@ -2249,12 +2338,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2264,17 +2353,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Night</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2283,19 +2372,22 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="K30" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>16000</v>
       </c>
     </row>
     <row r="31">
@@ -2311,12 +2403,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2326,17 +2418,17 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Night</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2345,19 +2437,22 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="K31" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>4000</v>
       </c>
     </row>
     <row r="32">
@@ -2378,7 +2473,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Night</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2388,12 +2483,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Night</t>
+          <t>Morning</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Morning</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2410,16 +2505,19 @@
         <v>40</v>
       </c>
       <c r="K32" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>20000</v>
       </c>
     </row>
     <row r="33">
@@ -2435,12 +2533,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Morning</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2450,12 +2548,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2469,19 +2567,22 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="K33" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>12000</v>
       </c>
     </row>
     <row r="34">
@@ -2502,12 +2603,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Night</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2517,12 +2618,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Morning</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Night</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2531,19 +2632,22 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="K34" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>8000</v>
       </c>
     </row>
     <row r="35">
@@ -2559,32 +2663,32 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Morning</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Night</t>
+          <t>Morning</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2593,19 +2697,22 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="K35" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>8000</v>
       </c>
     </row>
     <row r="36">
@@ -2621,53 +2728,56 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>Evening</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
           <t>Night</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Evening</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Off</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Morning</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Night</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Morning</t>
-        </is>
-      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>Off</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="K36" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>8000</v>
       </c>
     </row>
     <row r="37">
@@ -2683,22 +2793,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Night</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2708,28 +2818,31 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="J37" t="n">
         <v>32</v>
       </c>
       <c r="K37" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>16000</v>
       </c>
     </row>
   </sheetData>
